--- a/messy_supplier_data.xlsx
+++ b/messy_supplier_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC4"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,101 +467,6 @@
           <t>cost</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>part_number</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>item_name</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>group</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>make</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>measurement</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>net_weight</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>composition</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>finish</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>standards</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>retail_price</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>class</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>vendor</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>dims</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>material</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>color</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>certifications</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>msrp</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -612,162 +517,439 @@
       <c r="J2" t="n">
         <v>249.99</v>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>SKU-4402</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>HydroShield Waterproof Keyboard</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Peripherals</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>KeyForge</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>44 x 13 x 3.5 cm</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>850 g</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>ABS Plastic, Silicone Gaskets</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Gunmetal Grey</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>IP68, CE, FCC</t>
         </is>
       </c>
-      <c r="T3" t="n">
+      <c r="J3" t="n">
         <v>79.5</v>
       </c>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SKU-1189</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Precision Digital Vernier Caliper</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Measurement Tools</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ApexMeasure</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>25 x 8 x 2 cm</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>220 g</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>SKU-1189</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Precision Digital Vernier Caliper</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Measurement Tools</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>ApexMeasure</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>25 x 8 x 2 cm</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Hardened Stainless Steel</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>Silver / Black</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>NIST Traceable, DIN 862</t>
         </is>
       </c>
-      <c r="AC4" t="n">
+      <c r="J4" t="n">
         <v>45</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SKU-5099</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>UltraView 27-inch 4K Monitor</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Displays</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VisionTech</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>61 x 20 x 45 cm</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>5.2 kg</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Aluminum &amp; Recycled Plastic</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Space Gray</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Energy Star, RoHS</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SKU-7734</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Vertical Ergonomic Mouse</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Peripherals</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>KeyForge</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>12 x 8 x 7 cm</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Textured Rubber, ABS</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Charcoal</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>CE, FCC</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>29.99</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SKU-2044</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dual Motor Standing Desk</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Office Furniture</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>SteelWorks</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>150 x 75 x 70-120 cm</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>35 kg</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Bamboo Top, Steel Frame</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Natural Wood / White</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>UL, BIFMA</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SKU-8810</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>AeroNoise Cancelling Headphones</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Audio</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>SonicBoom</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>18 x 15 x 8 cm</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Vegan Leather, Memory Foam</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Midnight Blue</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>FCC, CE</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SKU-3120</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ProConnect 10-in-1 USB-C Hub</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TechLink</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>15 x 5 x 1.5 cm</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>150 g</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Anodized Aluminum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>RoHS, CE</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>59.99</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SKU-6652</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Foldable Aluminum Laptop Stand</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TechLink</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>24 x 23 x 0.4 cm</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>450 g</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Aircraft Grade Aluminum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Matte Silver</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="n">
+        <v>34.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SKU-9901</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Lumina True Wireless Earbuds</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Audio</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>SonicBoom</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>6 x 4 x 2.5 cm (Case)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>45 g</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Polycarbonate</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Gloss White</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>IPX5, CE</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>89</v>
       </c>
     </row>
   </sheetData>
